--- a/LoanOfficer-A/2023/135 thasana.xlsx
+++ b/LoanOfficer-A/2023/135 thasana.xlsx
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -838,8 +838,8 @@
         <v>1</v>
       </c>
       <c r="C2" s="11">
-        <f>G1*350</f>
-        <v>5950</v>
+        <f>G1*700</f>
+        <v>11900</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1*7</f>
-        <v>119</v>
+        <v>46020</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5950</v>
+        <v>9100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C3" s="4">
+        <v>700</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -900,9 +906,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45911</v>
+      </c>
+      <c r="C4" s="4">
+        <v>700</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -926,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45918</v>
+      </c>
+      <c r="C5" s="4">
+        <v>700</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -952,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45926</v>
+      </c>
+      <c r="C6" s="4">
+        <v>700</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>

--- a/LoanOfficer-A/2023/135 thasana.xlsx
+++ b/LoanOfficer-A/2023/135 thasana.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2800</v>
+        <v>4200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9100</v>
+        <v>7700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1002,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45935</v>
+      </c>
+      <c r="C7" s="4">
+        <v>700</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1028,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45942</v>
+      </c>
+      <c r="C8" s="4">
+        <v>700</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>

--- a/LoanOfficer-A/2023/135 thasana.xlsx
+++ b/LoanOfficer-A/2023/135 thasana.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4200</v>
+        <v>6300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7700</v>
+        <v>5600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1066,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45957</v>
+      </c>
+      <c r="C9" s="4">
+        <v>700</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1092,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45957</v>
+      </c>
+      <c r="C10" s="4">
+        <v>700</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1118,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45972</v>
+      </c>
+      <c r="C11" s="4">
+        <v>700</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
